--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5d60a861341b794a/Documents/GitHub/NewspaperDeliverySystem/user stories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC1177F-EFC3-434C-B6CD-7E704E29B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7EC1177F-EFC3-434C-B6CD-7E704E29B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7266095-2BC1-47AC-9309-D952ECA3A908}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
   <si>
     <t>Number</t>
   </si>
@@ -77,9 +77,6 @@
     <t>to correct any mistakes.</t>
   </si>
   <si>
-    <t>Cu</t>
-  </si>
-  <si>
     <t>Verify entered user exists</t>
   </si>
   <si>
@@ -273,6 +270,264 @@
   </si>
   <si>
     <t>Verify the news agent not being able to restock the correct publication generates an errror message</t>
+  </si>
+  <si>
+    <t>Orders - User Stories</t>
+  </si>
+  <si>
+    <t>Order - AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.As a news agent, </t>
+  </si>
+  <si>
+    <t>Verify the entered customer exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to place an order for newspapers to be delivered </t>
+  </si>
+  <si>
+    <t>Verify the entered publication exists.</t>
+  </si>
+  <si>
+    <t>as the customer has asked to receive newspapers regularly.</t>
+  </si>
+  <si>
+    <t>Verify the order ID is unique.</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is not left empty.</t>
+  </si>
+  <si>
+    <t>Verify the publication ID is not left empty.</t>
+  </si>
+  <si>
+    <t>Verify a delivery pattern has been entered.</t>
+  </si>
+  <si>
+    <t>Verify the delivery pattern contains valid delivery days.</t>
+  </si>
+  <si>
+    <t>Verify the new order is successfully saved to the database.</t>
+  </si>
+  <si>
+    <t>Verify an invalid customer generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify an invalid publication generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify an empty customer ID generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify an empty publication ID generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify an invalid or empty delivery pattern generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify a duplicate order ID generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify the order not being successfully saved generates an error message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.As a news agent, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to be able to see what publications the customer is receiving </t>
+  </si>
+  <si>
+    <t>Verify the correct orders for the customer are retrieved.</t>
+  </si>
+  <si>
+    <t>because I want to remind myself of what publications they ordered.</t>
+  </si>
+  <si>
+    <t>Verify the correct publication ID is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the correct customer ID is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the correct delivery pattern is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify only orders belonging to the entered customer are displayed.</t>
+  </si>
+  <si>
+    <t>Verify a customer with no existing orders generates an appropriate message.</t>
+  </si>
+  <si>
+    <t>Verify an order that does not exist generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify missing order information generates an error message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.As a news agent, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to update an order </t>
+  </si>
+  <si>
+    <t>Verify the entered order exists.</t>
+  </si>
+  <si>
+    <t>because a customer has changed their mind on what publication to receive.</t>
+  </si>
+  <si>
+    <t>Verify the newly entered publication exists.</t>
+  </si>
+  <si>
+    <t>Verify the delivery pattern is valid.</t>
+  </si>
+  <si>
+    <t>Verify the order remains associated with the correct customer.</t>
+  </si>
+  <si>
+    <t>Verify the order is successfully updated with the new information.</t>
+  </si>
+  <si>
+    <t>Verify a publication that does not exist generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify the order not being successfully updated generates an error message.</t>
+  </si>
+  <si>
+    <t>4.As a news agent,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I want to delete an order </t>
+  </si>
+  <si>
+    <t>as the customer accidentally ordered a publication.</t>
+  </si>
+  <si>
+    <t>Verify the order belongs to the entered customer.</t>
+  </si>
+  <si>
+    <t>Verify the correct order is successfully deleted from the database.</t>
+  </si>
+  <si>
+    <t>Verify the deleted order can no longer be retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the customer remains in the database after the order is deleted.</t>
+  </si>
+  <si>
+    <t>Verify an order belonging to another customer cannot be deleted.</t>
+  </si>
+  <si>
+    <t>Verify the order not being successfully deleted generates an error message.</t>
+  </si>
+  <si>
+    <t>Customer - US</t>
+  </si>
+  <si>
+    <t>Cust - AC</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to create a new customer </t>
+  </si>
+  <si>
+    <t>Verify the customer name is not left empty.</t>
+  </si>
+  <si>
+    <t>because a new local customer wants me to deliver newspapers.</t>
+  </si>
+  <si>
+    <t>Verify the customer name has a minimum of 1 character.</t>
+  </si>
+  <si>
+    <t>Verify the customer address is not left empty.</t>
+  </si>
+  <si>
+    <t>Verify the customer contact details are not left empty.</t>
+  </si>
+  <si>
+    <t>Verify the new customer is successfully saved to the database.</t>
+  </si>
+  <si>
+    <t>Verify an empty name field generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify an empty address field generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify empty contact details generate an error message.</t>
+  </si>
+  <si>
+    <t>Verify a duplicate customer ID generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify the customer not being successfully saved generates an error message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to update a customer's details </t>
+  </si>
+  <si>
+    <t>so that any deliveries are delivered to them correctly.</t>
+  </si>
+  <si>
+    <t>Verify the customer's details are successfully updated in the database.</t>
+  </si>
+  <si>
+    <t>Verify a customer that does not exist generates an error message.</t>
+  </si>
+  <si>
+    <t>Verify the customer not being successfully updated generates an error message.</t>
+  </si>
+  <si>
+    <t>3.As a news agent,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I want to be able to see a customer's details </t>
+  </si>
+  <si>
+    <t>Verify the correct customer is retrieved.</t>
+  </si>
+  <si>
+    <t>to ensure if they are correct.</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the customer's name is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the customer's address is retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the customer's contact details are retrieved.</t>
+  </si>
+  <si>
+    <t>Verify missing customer details generate an error message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.As a news agent, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to delete a customer's account </t>
+  </si>
+  <si>
+    <t>Verify the correct customer is selected for deletion.</t>
+  </si>
+  <si>
+    <t>as they no longer wish to receive newspapers regularly.</t>
+  </si>
+  <si>
+    <t>Verify the customer is successfully deleted from the database.</t>
+  </si>
+  <si>
+    <t>Verify the deleted customer can no longer be retrieved.</t>
+  </si>
+  <si>
+    <t>Verify the customer not being successfully deleted generates an error message.</t>
   </si>
 </sst>
 </file>
@@ -648,13 +903,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6669703-D861-4853-A03C-2BD7E616836D}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,7 +920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -673,61 +928,61 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -735,31 +990,31 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -767,51 +1022,51 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -819,38 +1074,38 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>21</v>
       </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>22</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -860,21 +1115,521 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1FDFD2-DDDE-4B64-B452-BAE227FEA908}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultColWidth="77.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA3C9B1-67AE-4FC3-9A3C-0CAB1ECF3271}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="65.42578125" customWidth="1"/>
+    <col min="2" max="2" width="71.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>125</v>
+      </c>
+      <c r="B1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -885,13 +1640,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D878139E-7EB3-4925-9F6E-43018AC46F66}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="85.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -902,274 +1657,274 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>3</v>
       </c>
       <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>3</v>
       </c>
       <c r="C22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C31" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C35" t="s">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C41" t="s">
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" t="s">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C48" t="s">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" t="s">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1935,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3B0FF-370B-4D26-9C5F-A03D18CBAD5F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1189,7 +1944,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CBA472-5F67-4E03-9BD0-AEC7A8404DF5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1198,7 +1953,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976F6F6C-4BF2-4009-9A4D-82FF59E3879F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7EC1177F-EFC3-434C-B6CD-7E704E29B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7266095-2BC1-47AC-9309-D952ECA3A908}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -583,6 +583,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5d60a861341b794a/Documents/GitHub/NewspaperDeliverySystem/user stories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7EC1177F-EFC3-434C-B6CD-7E704E29B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7266095-2BC1-47AC-9309-D952ECA3A908}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6BD752-0800-4D0D-847C-D9DA7FE3FD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="190">
   <si>
     <t>Number</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Verify entered publications not existing generates error message</t>
   </si>
   <si>
-    <t>Verify the newly etered publications do exist</t>
-  </si>
-  <si>
     <t>Verify bill not found generates an error message</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>Verify that the correct bills were retrieved</t>
   </si>
   <si>
-    <t>Verify not corret bill being retrieved generates an erros message</t>
-  </si>
-  <si>
     <t>Verify the entered publications were purchased by the user</t>
   </si>
   <si>
@@ -528,6 +522,99 @@
   </si>
   <si>
     <t>Verify the customer not being successfully deleted generates an error message.</t>
+  </si>
+  <si>
+    <t>As a news agent,</t>
+  </si>
+  <si>
+    <t>I want to create a new docket</t>
+  </si>
+  <si>
+    <t>to hand out to delivery person</t>
+  </si>
+  <si>
+    <t>I want to read a delivery docket</t>
+  </si>
+  <si>
+    <t>to insure the information is correct</t>
+  </si>
+  <si>
+    <t>I want to update a delivery docket</t>
+  </si>
+  <si>
+    <t>to add any changes that may occur</t>
+  </si>
+  <si>
+    <t>to remove previously delivered dockets</t>
+  </si>
+  <si>
+    <t>Verify the entered delivery docket exists</t>
+  </si>
+  <si>
+    <t>Verify the delivery docket is succesfully deleted from the database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the delivery docket not being deleted correctly shows an error message </t>
+  </si>
+  <si>
+    <t>Verify that invalid delivery docket generates an error message</t>
+  </si>
+  <si>
+    <t>Verify that an incorrectly deleted delivery docket generates an error message</t>
+  </si>
+  <si>
+    <t>I want to delete a delivery docket</t>
+  </si>
+  <si>
+    <t>Verify the delivery docket that was entered exists</t>
+  </si>
+  <si>
+    <t>Verify the correct delivery docket was retreived</t>
+  </si>
+  <si>
+    <t>Verify that an incorrect delivery docket returns an error</t>
+  </si>
+  <si>
+    <t>Verify not correct bill being retrieved generates an error message</t>
+  </si>
+  <si>
+    <t>Verify that invalid delivery docket returns an error message</t>
+  </si>
+  <si>
+    <t>Verify already existing delivery docket returns error</t>
+  </si>
+  <si>
+    <t>Verify the delivery docket ID is unique</t>
+  </si>
+  <si>
+    <t>Verify the new delivery docket not being successfully added generates an error message</t>
+  </si>
+  <si>
+    <t>Verify the delivery docket not being correctly updated generates an error message</t>
+  </si>
+  <si>
+    <t>Verify the delivery docket is correctly saved in the database</t>
+  </si>
+  <si>
+    <t>Verify an empty order ID generates an error message</t>
+  </si>
+  <si>
+    <t>Verify an empty customer ID generates an error message</t>
+  </si>
+  <si>
+    <t>Verify the order ID is not left empty</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is not left empty</t>
+  </si>
+  <si>
+    <t>Verify the newly entered publications do exist</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is a valid ID</t>
+  </si>
+  <si>
+    <t>Verify the order ID is a valid ID</t>
   </si>
 </sst>
 </file>
@@ -583,10 +670,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -906,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6669703-D861-4853-A03C-2BD7E616836D}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
@@ -948,17 +1031,17 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -978,138 +1061,138 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>2</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>9</v>
       </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>4</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>3</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
         <v>21</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1124,283 +1207,283 @@
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1419,221 +1502,221 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1666,78 +1749,78 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -1745,28 +1828,28 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -1774,83 +1857,83 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
@@ -1858,77 +1941,77 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1938,9 +2021,208 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3B0FF-370B-4D26-9C5F-A03D18CBAD5F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="52.5703125" customWidth="1"/>
+    <col min="3" max="3" width="88.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nandi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6BD752-0800-4D0D-847C-D9DA7FE3FD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9706DF-EAC8-4C12-AA07-7137D0FCC6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="271">
   <si>
     <t>Number</t>
   </si>
@@ -615,16 +615,265 @@
   </si>
   <si>
     <t>Verify the order ID is a valid ID</t>
+  </si>
+  <si>
+    <t>Test Design Table</t>
+  </si>
+  <si>
+    <t>Test Number</t>
+  </si>
+  <si>
+    <t>Test Objective</t>
+  </si>
+  <si>
+    <t>Input(s)</t>
+  </si>
+  <si>
+    <t>Expected Output(s)</t>
+  </si>
+  <si>
+    <t>TC01</t>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>TC08</t>
+  </si>
+  <si>
+    <t>TC09</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t>Verify the customer name is accepted when 1 character long.</t>
+  </si>
+  <si>
+    <t>Verify the customer name is accepted when more 1 character long.</t>
+  </si>
+  <si>
+    <t>Verify the is rejected when customer name is not left empty.</t>
+  </si>
+  <si>
+    <t>Verify the customer address is accepted when 1 character long.</t>
+  </si>
+  <si>
+    <t>Verify the customer address is accepted when more 1 character long.</t>
+  </si>
+  <si>
+    <t>Verify the is rejected when customer address is not left empty.</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is accepted when its unique</t>
+  </si>
+  <si>
+    <t>Verify the customer ID is rejected when its not unique</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with invalid first name</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with invalid address</t>
+  </si>
+  <si>
+    <t>Verify customer account is saved to database when all details are valid</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with invalid contact details</t>
+  </si>
+  <si>
+    <t>Verify contact details is accepted when exactly 10 digits</t>
+  </si>
+  <si>
+    <t>Verify contact details is rejected when fewer than 10 digits</t>
+  </si>
+  <si>
+    <t>Verify contact details is rejected when more than 10 digits</t>
+  </si>
+  <si>
+    <t>Verify contact details is rejected when containing alphabetic characters</t>
+  </si>
+  <si>
+    <t>Verify the customer address has a minimum of 1 character.</t>
+  </si>
+  <si>
+    <t>Customer Name = ""</t>
+  </si>
+  <si>
+    <t>Customer Name = "A"</t>
+  </si>
+  <si>
+    <t>Customer Name = "Arnold"</t>
+  </si>
+  <si>
+    <t>Customer Address = ""</t>
+  </si>
+  <si>
+    <t>Customer Address = "A"</t>
+  </si>
+  <si>
+    <t>Customer Address = "Athlone"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer ID = "2" CustomerIDs=[1] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer ID = "2" CustomerIDs=[1,2] </t>
+  </si>
+  <si>
+    <t>Contact Details = "0872918648"</t>
+  </si>
+  <si>
+    <t>Contact Details = "087291868"</t>
+  </si>
+  <si>
+    <t>Contact Details = "0872842918648"</t>
+  </si>
+  <si>
+    <t>Contact Details = "0872A18648"</t>
+  </si>
+  <si>
+    <t>Arnold,Athlone,2,0872918648</t>
+  </si>
+  <si>
+    <t>"",Athlone,2,0872918648</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with invalid userID</t>
+  </si>
+  <si>
+    <t>Arnold,"",2,0872918648</t>
+  </si>
+  <si>
+    <t>Arnold,Athlone,"",0872918648</t>
+  </si>
+  <si>
+    <t>Arnold,Athlone,2,""</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with dublicate userID</t>
+  </si>
+  <si>
+    <t>Customer name accepted</t>
+  </si>
+  <si>
+    <t>Error message: Invalid Customer Name</t>
+  </si>
+  <si>
+    <t>Error message: Dublicate ID</t>
+  </si>
+  <si>
+    <t>Customer address accepted</t>
+  </si>
+  <si>
+    <t>Customer ID accepted</t>
+  </si>
+  <si>
+    <t>Contact Details Accepted</t>
+  </si>
+  <si>
+    <t>Error message: Invalid Contact Details</t>
+  </si>
+  <si>
+    <t>Customer Account saved to database successfully</t>
+  </si>
+  <si>
+    <t>Customer Account not created</t>
+  </si>
+  <si>
+    <t>Boundary Test Values</t>
+  </si>
+  <si>
+    <t>Valid Equivalance Class Test</t>
+  </si>
+  <si>
+    <t>Invalid Equivalance Class Test</t>
+  </si>
+  <si>
+    <t>Integration/End to End Test</t>
+  </si>
+  <si>
+    <t>Invalid Phone number formats</t>
+  </si>
+  <si>
+    <t>Blank Values</t>
+  </si>
+  <si>
+    <t>Verify Normal Values are accepted</t>
+  </si>
+  <si>
+    <t>Succesfull save to database</t>
+  </si>
+  <si>
+    <t>Account Creation fails when required fields is invalid</t>
+  </si>
+  <si>
+    <t>Phone number below or above boundary</t>
+  </si>
+  <si>
+    <t>Phone number exactly 10 digits long</t>
+  </si>
+  <si>
+    <t>Address minimum boundary of 1 char</t>
+  </si>
+  <si>
+    <t>name minimum boundary of 1 char</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -650,10 +899,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1493,14 +1748,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA3C9B1-67AE-4FC3-9A3C-0CAB1ECF3271}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.42578125" customWidth="1"/>
     <col min="2" max="2" width="71.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>123</v>
       </c>
@@ -1508,218 +1767,606 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G3" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>126</v>
       </c>
       <c r="B4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
       <c r="B5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" t="s">
+        <v>232</v>
+      </c>
+      <c r="J6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" t="s">
+        <v>230</v>
+      </c>
+      <c r="J7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="G8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="G9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="G10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I10" t="s">
+        <v>233</v>
+      </c>
+      <c r="J10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="G11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="G12" t="s">
+        <v>202</v>
+      </c>
+      <c r="H12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" t="s">
+        <v>237</v>
+      </c>
+      <c r="J12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="G13" t="s">
+        <v>203</v>
+      </c>
+      <c r="H13" t="s">
+        <v>225</v>
+      </c>
+      <c r="I13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="G14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" t="s">
+        <v>227</v>
+      </c>
+      <c r="I15" t="s">
+        <v>240</v>
+      </c>
+      <c r="J15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>93</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="G16" t="s">
+        <v>206</v>
+      </c>
+      <c r="H16" t="s">
+        <v>228</v>
+      </c>
+      <c r="I16" t="s">
+        <v>241</v>
+      </c>
+      <c r="J16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>138</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="G17" t="s">
+        <v>207</v>
+      </c>
+      <c r="H17" t="s">
+        <v>223</v>
+      </c>
+      <c r="I17" t="s">
+        <v>242</v>
+      </c>
+      <c r="J17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>139</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="G18" t="s">
+        <v>208</v>
+      </c>
+      <c r="H18" t="s">
+        <v>221</v>
+      </c>
+      <c r="I18" t="s">
+        <v>243</v>
+      </c>
+      <c r="J18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="G19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H19" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" t="s">
+        <v>245</v>
+      </c>
+      <c r="J19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="G20" t="s">
+        <v>210</v>
+      </c>
+      <c r="H20" t="s">
+        <v>244</v>
+      </c>
+      <c r="I20" t="s">
+        <v>246</v>
+      </c>
+      <c r="J20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="G21" t="s">
+        <v>211</v>
+      </c>
+      <c r="H21" t="s">
+        <v>248</v>
+      </c>
+      <c r="I21" t="s">
+        <v>242</v>
+      </c>
+      <c r="J21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+      <c r="G22" t="s">
+        <v>212</v>
+      </c>
+      <c r="H22" t="s">
+        <v>224</v>
+      </c>
+      <c r="I22" t="s">
+        <v>247</v>
+      </c>
+      <c r="J22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>143</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="G27" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>144</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="G28" t="s">
+        <v>198</v>
+      </c>
+      <c r="H28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>146</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="G29" t="s">
+        <v>203</v>
+      </c>
+      <c r="H29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+      <c r="G30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+      <c r="G31" t="s">
+        <v>205</v>
+      </c>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G35" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>152</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="G36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>153</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="G37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>155</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+      <c r="G38" t="s">
+        <v>201</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
+      <c r="G39" t="s">
+        <v>202</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>158</v>
       </c>
+      <c r="G41" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>205</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>206</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>207</v>
+      </c>
+      <c r="H52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>208</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>209</v>
+      </c>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>210</v>
+      </c>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>211</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>212</v>
+      </c>
+      <c r="H57" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H36:H39"/>
+    <mergeCell ref="H53:H57"/>
+    <mergeCell ref="H30:H31"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nandi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9706DF-EAC8-4C12-AA07-7137D0FCC6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB07269-A642-4864-B8C2-75927A617778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="3015" yWindow="7155" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="272">
   <si>
     <t>Number</t>
   </si>
@@ -692,9 +692,6 @@
     <t>Verify the customer name is accepted when more 1 character long.</t>
   </si>
   <si>
-    <t>Verify the is rejected when customer name is not left empty.</t>
-  </si>
-  <si>
     <t>Verify the customer address is accepted when 1 character long.</t>
   </si>
   <si>
@@ -858,6 +855,12 @@
   </si>
   <si>
     <t>name minimum boundary of 1 char</t>
+  </si>
+  <si>
+    <t>Verify the customer contact details have a minimum of 1 character.</t>
+  </si>
+  <si>
+    <t>Verify the customer name is rejected when customer name is not left empty.</t>
   </si>
 </sst>
 </file>
@@ -1753,9 +1756,9 @@
   <cols>
     <col min="1" max="1" width="65.42578125" customWidth="1"/>
     <col min="2" max="2" width="71.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="65.42578125" customWidth="1"/>
+    <col min="9" max="9" width="41" customWidth="1"/>
     <col min="10" max="10" width="45.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1815,10 +1818,10 @@
         <v>213</v>
       </c>
       <c r="I5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1832,27 +1835,27 @@
         <v>214</v>
       </c>
       <c r="I6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G7" t="s">
         <v>197</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>271</v>
       </c>
       <c r="I7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1863,335 +1866,335 @@
         <v>198</v>
       </c>
       <c r="H8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>132</v>
+        <v>270</v>
       </c>
       <c r="G9" t="s">
         <v>199</v>
       </c>
       <c r="H9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
         <v>200</v>
       </c>
       <c r="H10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G11" t="s">
         <v>201</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G12" t="s">
         <v>202</v>
       </c>
       <c r="H12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G13" t="s">
         <v>203</v>
       </c>
       <c r="H13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G14" t="s">
         <v>204</v>
       </c>
       <c r="H14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
       <c r="G15" t="s">
         <v>205</v>
       </c>
       <c r="H15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
       <c r="G16" t="s">
         <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
         <v>207</v>
       </c>
       <c r="H17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
         <v>208</v>
       </c>
       <c r="H18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>139</v>
+      </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G19" t="s">
         <v>209</v>
       </c>
       <c r="H19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
         <v>210</v>
       </c>
       <c r="H20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s">
         <v>211</v>
       </c>
       <c r="H21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G22" t="s">
         <v>212</v>
       </c>
       <c r="H22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
       <c r="G27" t="s">
         <v>195</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
         <v>198</v>
       </c>
       <c r="H28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
         <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>146</v>
+      </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G30" t="s">
         <v>204</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G31" t="s">
         <v>205</v>
@@ -2200,44 +2203,41 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>152</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
       <c r="G36" t="s">
         <v>196</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
         <v>199</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G38" t="s">
         <v>201</v>
@@ -2257,8 +2257,11 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>155</v>
+      </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G39" t="s">
         <v>202</v>
@@ -2267,23 +2270,26 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>158</v>
       </c>
-      <c r="G41" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G42" t="s">
         <v>197</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2297,7 +2303,7 @@
         <v>204</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2314,7 +2320,7 @@
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
@@ -2322,7 +2328,7 @@
         <v>207</v>
       </c>
       <c r="H52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.25">
@@ -2330,7 +2336,7 @@
         <v>208</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.25">

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB07269-A642-4864-B8C2-75927A617778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910DA472-3C47-4606-A043-C5821AC1A7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="7155" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="3045" yWindow="7125" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -770,27 +770,6 @@
     <t>Contact Details = "0872A18648"</t>
   </si>
   <si>
-    <t>Arnold,Athlone,2,0872918648</t>
-  </si>
-  <si>
-    <t>"",Athlone,2,0872918648</t>
-  </si>
-  <si>
-    <t>Verify customer account creation fails with invalid userID</t>
-  </si>
-  <si>
-    <t>Arnold,"",2,0872918648</t>
-  </si>
-  <si>
-    <t>Arnold,Athlone,"",0872918648</t>
-  </si>
-  <si>
-    <t>Arnold,Athlone,2,""</t>
-  </si>
-  <si>
-    <t>Verify customer account creation fails with dublicate userID</t>
-  </si>
-  <si>
     <t>Customer name accepted</t>
   </si>
   <si>
@@ -861,6 +840,27 @@
   </si>
   <si>
     <t>Verify the customer name is rejected when customer name is not left empty.</t>
+  </si>
+  <si>
+    <t>"Arnold","Athlone",2,"0872918648"</t>
+  </si>
+  <si>
+    <t>"","Athlone",2,"0872918648"</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with invalid CustomerID</t>
+  </si>
+  <si>
+    <t>Verify customer account creation fails with dublicate CustomerID</t>
+  </si>
+  <si>
+    <t>"Arnold","",2,"0872918648"</t>
+  </si>
+  <si>
+    <t>"Arnold","Athlone",null,"0872918648"</t>
+  </si>
+  <si>
+    <t>"Arnold","Athlone",2,""</t>
   </si>
 </sst>
 </file>
@@ -1821,7 +1821,7 @@
         <v>230</v>
       </c>
       <c r="J5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
         <v>231</v>
       </c>
       <c r="J6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1849,13 +1849,13 @@
         <v>197</v>
       </c>
       <c r="H7" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I7" t="s">
         <v>229</v>
       </c>
       <c r="J7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1872,12 +1872,12 @@
         <v>233</v>
       </c>
       <c r="J8" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G9" t="s">
         <v>199</v>
@@ -1889,7 +1889,7 @@
         <v>234</v>
       </c>
       <c r="J9" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1906,7 +1906,7 @@
         <v>232</v>
       </c>
       <c r="J10" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1923,7 +1923,7 @@
         <v>235</v>
       </c>
       <c r="J11" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
         <v>236</v>
       </c>
       <c r="J12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1957,7 +1957,7 @@
         <v>237</v>
       </c>
       <c r="J13" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1974,7 +1974,7 @@
         <v>238</v>
       </c>
       <c r="J14" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
         <v>239</v>
       </c>
       <c r="J15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2005,7 +2005,7 @@
         <v>240</v>
       </c>
       <c r="J16" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2022,10 +2022,10 @@
         <v>222</v>
       </c>
       <c r="I17" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="J17" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>220</v>
       </c>
       <c r="I18" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="J18" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2062,10 +2062,10 @@
         <v>221</v>
       </c>
       <c r="I19" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="J19" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,13 +2076,13 @@
         <v>210</v>
       </c>
       <c r="H20" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="I20" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J20" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2093,13 +2093,13 @@
         <v>211</v>
       </c>
       <c r="H21" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="I21" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="J21" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2113,10 +2113,10 @@
         <v>223</v>
       </c>
       <c r="I22" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="J22" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2139,7 +2139,7 @@
         <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2147,7 +2147,7 @@
         <v>195</v>
       </c>
       <c r="H27" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2161,7 +2161,7 @@
         <v>198</v>
       </c>
       <c r="H28" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2175,7 +2175,7 @@
         <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,7 +2189,7 @@
         <v>204</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2221,7 +2221,7 @@
         <v>151</v>
       </c>
       <c r="G35" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -2229,7 +2229,7 @@
         <v>196</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -2278,7 +2278,7 @@
         <v>141</v>
       </c>
       <c r="G41" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>197</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2303,7 +2303,7 @@
         <v>204</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2320,7 +2320,7 @@
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>207</v>
       </c>
       <c r="H52" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.25">
@@ -2336,7 +2336,7 @@
         <v>208</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.25">

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910DA472-3C47-4606-A043-C5821AC1A7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC8F516-982D-46D9-AEA2-83F79C365EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="7125" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
+    <workbookView xWindow="1440" yWindow="2865" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill" sheetId="1" r:id="rId1"/>
@@ -857,10 +857,10 @@
     <t>"Arnold","",2,"0872918648"</t>
   </si>
   <si>
-    <t>"Arnold","Athlone",null,"0872918648"</t>
-  </si>
-  <si>
     <t>"Arnold","Athlone",2,""</t>
+  </si>
+  <si>
+    <t>"Arnold","Athlone",0,"0872918648"</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2079,7 @@
         <v>267</v>
       </c>
       <c r="I20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J20" t="s">
         <v>249</v>
@@ -2113,7 +2113,7 @@
         <v>223</v>
       </c>
       <c r="I22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J22" t="s">
         <v>249</v>

--- a/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
+++ b/user stories/NewsPaperDeliverySystem User Stories and Acceptence Criteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\NewspaperDeliverySystem\user stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC8F516-982D-46D9-AEA2-83F79C365EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9135373-68CB-4BD4-B4AA-40D71ABC7766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="2865" windowWidth="25785" windowHeight="10245" activeTab="2" xr2:uid="{6307955D-1D03-43DF-8C9F-06C76E88F2E1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="263">
   <si>
     <t>Number</t>
   </si>
@@ -701,12 +701,6 @@
     <t>Verify the is rejected when customer address is not left empty.</t>
   </si>
   <si>
-    <t>Verify the customer ID is accepted when its unique</t>
-  </si>
-  <si>
-    <t>Verify the customer ID is rejected when its not unique</t>
-  </si>
-  <si>
     <t>Verify customer account creation fails with invalid first name</t>
   </si>
   <si>
@@ -752,12 +746,6 @@
     <t>Customer Address = "Athlone"</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer ID = "2" CustomerIDs=[1] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer ID = "2" CustomerIDs=[1,2] </t>
-  </si>
-  <si>
     <t>Contact Details = "0872918648"</t>
   </si>
   <si>
@@ -776,15 +764,9 @@
     <t>Error message: Invalid Customer Name</t>
   </si>
   <si>
-    <t>Error message: Dublicate ID</t>
-  </si>
-  <si>
     <t>Customer address accepted</t>
   </si>
   <si>
-    <t>Customer ID accepted</t>
-  </si>
-  <si>
     <t>Contact Details Accepted</t>
   </si>
   <si>
@@ -842,25 +824,16 @@
     <t>Verify the customer name is rejected when customer name is not left empty.</t>
   </si>
   <si>
-    <t>"Arnold","Athlone",2,"0872918648"</t>
-  </si>
-  <si>
-    <t>"","Athlone",2,"0872918648"</t>
-  </si>
-  <si>
-    <t>Verify customer account creation fails with invalid CustomerID</t>
-  </si>
-  <si>
-    <t>Verify customer account creation fails with dublicate CustomerID</t>
-  </si>
-  <si>
-    <t>"Arnold","",2,"0872918648"</t>
-  </si>
-  <si>
-    <t>"Arnold","Athlone",2,""</t>
-  </si>
-  <si>
-    <t>"Arnold","Athlone",0,"0872918648"</t>
+    <t>"Arnold","Athlone",""</t>
+  </si>
+  <si>
+    <t>"Arnold","","0872918648"</t>
+  </si>
+  <si>
+    <t>"","Athlone","0872918648"</t>
+  </si>
+  <si>
+    <t>"Arnold","Athlone","0872918648"</t>
   </si>
 </sst>
 </file>
@@ -1818,10 +1791,10 @@
         <v>213</v>
       </c>
       <c r="I5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1835,27 +1808,27 @@
         <v>214</v>
       </c>
       <c r="I6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G7" t="s">
         <v>197</v>
       </c>
       <c r="H7" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1869,15 +1842,15 @@
         <v>215</v>
       </c>
       <c r="I8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G9" t="s">
         <v>199</v>
@@ -1886,10 +1859,10 @@
         <v>216</v>
       </c>
       <c r="I9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1903,10 +1876,10 @@
         <v>217</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1917,13 +1890,13 @@
         <v>201</v>
       </c>
       <c r="H11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J11" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1934,13 +1907,13 @@
         <v>202</v>
       </c>
       <c r="H12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1954,10 +1927,10 @@
         <v>224</v>
       </c>
       <c r="I13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,10 +1944,10 @@
         <v>225</v>
       </c>
       <c r="I14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J14" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1985,13 +1958,13 @@
         <v>205</v>
       </c>
       <c r="H15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I15" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="J15" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1999,13 +1972,13 @@
         <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="I16" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="J16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,13 +1992,13 @@
         <v>207</v>
       </c>
       <c r="H17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I17" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2039,13 +2012,13 @@
         <v>208</v>
       </c>
       <c r="H18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J18" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2055,69 +2028,21 @@
       <c r="B19" t="s">
         <v>130</v>
       </c>
-      <c r="G19" t="s">
-        <v>209</v>
-      </c>
-      <c r="H19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" t="s">
-        <v>269</v>
-      </c>
-      <c r="J19" t="s">
-        <v>249</v>
-      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>131</v>
       </c>
-      <c r="G20" t="s">
-        <v>210</v>
-      </c>
-      <c r="H20" t="s">
-        <v>267</v>
-      </c>
-      <c r="I20" t="s">
-        <v>271</v>
-      </c>
-      <c r="J20" t="s">
-        <v>249</v>
-      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>140</v>
       </c>
-      <c r="G21" t="s">
-        <v>211</v>
-      </c>
-      <c r="H21" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" t="s">
-        <v>265</v>
-      </c>
-      <c r="J21" t="s">
-        <v>249</v>
-      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>141</v>
       </c>
-      <c r="G22" t="s">
-        <v>212</v>
-      </c>
-      <c r="H22" t="s">
-        <v>223</v>
-      </c>
-      <c r="I22" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" t="s">
-        <v>249</v>
-      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
@@ -2139,7 +2064,7 @@
         <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2147,7 +2072,7 @@
         <v>195</v>
       </c>
       <c r="H27" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2161,7 +2086,7 @@
         <v>198</v>
       </c>
       <c r="H28" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2175,7 +2100,7 @@
         <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,7 +2114,7 @@
         <v>204</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2221,7 +2146,7 @@
         <v>151</v>
       </c>
       <c r="G35" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -2229,7 +2154,7 @@
         <v>196</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -2278,7 +2203,7 @@
         <v>141</v>
       </c>
       <c r="G41" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -2289,7 +2214,7 @@
         <v>197</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2303,7 +2228,7 @@
         <v>204</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2320,7 +2245,7 @@
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
@@ -2328,7 +2253,7 @@
         <v>207</v>
       </c>
       <c r="H52" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.25">
@@ -2336,7 +2261,7 @@
         <v>208</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.25">
